--- a/game36/web.xlsx
+++ b/game36/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19425" windowHeight="11850"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet5" sheetId="10" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="189">
   <si>
     <t>domain</t>
   </si>
@@ -50,7 +50,64 @@
     <t>json</t>
   </si>
   <si>
-    <t>eclithor.com</t>
+    <t>quaternion.fun</t>
+  </si>
+  <si>
+    <t>#8abe98</t>
+  </si>
+  <si>
+    <t>#e2e1dd</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>globalfinly.com</t>
+  </si>
+  <si>
+    <t>#ffd9a3</t>
+  </si>
+  <si>
+    <t>investwisey.com</t>
+  </si>
+  <si>
+    <t>#f597ba</t>
+  </si>
+  <si>
+    <t>moneyvaultx.com</t>
+  </si>
+  <si>
+    <t>#98b0ca</t>
+  </si>
+  <si>
+    <t>marketchk.com</t>
+  </si>
+  <si>
+    <t>#bdd0c4</t>
+  </si>
+  <si>
+    <t>spuddles.fun</t>
+  </si>
+  <si>
+    <t>#707899</t>
+  </si>
+  <si>
+    <t>moilfuns.fun</t>
+  </si>
+  <si>
+    <t>#70c588</t>
+  </si>
+  <si>
+    <t>play.seatranquil.com</t>
+  </si>
+  <si>
+    <t>#6b496a</t>
+  </si>
+  <si>
+    <t>sec.seatranquil.com</t>
+  </si>
+  <si>
+    <t>#e6e3c3</t>
   </si>
   <si>
     <t>#4167b1</t>
@@ -59,91 +116,16 @@
     <t>#def0f9</t>
   </si>
   <si>
-    <t>frogmore.fun</t>
-  </si>
-  <si>
     <t>#d62828</t>
   </si>
   <si>
     <t>#f8e9a1</t>
   </si>
   <si>
-    <t>pinnekjott.site</t>
-  </si>
-  <si>
     <t>#e58889</t>
   </si>
   <si>
     <t>#f9f0ed</t>
-  </si>
-  <si>
-    <t>taffeta.cloud</t>
-  </si>
-  <si>
-    <t>#b57743</t>
-  </si>
-  <si>
-    <t>#ebdec6</t>
-  </si>
-  <si>
-    <t>ruching.cloud</t>
-  </si>
-  <si>
-    <t>#a61b29</t>
-  </si>
-  <si>
-    <t>#f7ece7</t>
-  </si>
-  <si>
-    <t>color</t>
-  </si>
-  <si>
-    <t>globalfinly.com</t>
-  </si>
-  <si>
-    <t>#ffd9a3</t>
-  </si>
-  <si>
-    <t>investwisey.com</t>
-  </si>
-  <si>
-    <t>#f597ba</t>
-  </si>
-  <si>
-    <t>moneyvaultx.com</t>
-  </si>
-  <si>
-    <t>#98b0ca</t>
-  </si>
-  <si>
-    <t>marketchk.com</t>
-  </si>
-  <si>
-    <t>#bdd0c4</t>
-  </si>
-  <si>
-    <t>spuddles.fun</t>
-  </si>
-  <si>
-    <t>#707899</t>
-  </si>
-  <si>
-    <t>moilfuns.fun</t>
-  </si>
-  <si>
-    <t>#70c588</t>
-  </si>
-  <si>
-    <t>play.seatranquil.com</t>
-  </si>
-  <si>
-    <t>#6b496a</t>
-  </si>
-  <si>
-    <t>sec.seatranquil.com</t>
-  </si>
-  <si>
-    <t>#e6e3c3</t>
   </si>
   <si>
     <t>水性树脂改性机理及特性配伍总表（高清图谱版）</t>
@@ -630,7 +612,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="45">
+  <fonts count="44">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -800,14 +782,6 @@
     <font>
       <u/>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
       <color rgb="FF2972F4"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -957,7 +931,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="64">
+  <fills count="66">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1123,6 +1097,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF70C588"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ABE98"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E1DD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1494,85 +1480,79 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="34" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="35" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="35" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="36" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="36" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="37" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="37" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1581,10 +1561,10 @@
     <xf numFmtId="0" fontId="43" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1593,10 +1573,10 @@
     <xf numFmtId="0" fontId="43" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1605,10 +1585,10 @@
     <xf numFmtId="0" fontId="43" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1617,10 +1597,10 @@
     <xf numFmtId="0" fontId="43" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1629,17 +1609,23 @@
     <xf numFmtId="0" fontId="43" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1771,9 +1757,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1813,9 +1796,6 @@
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1828,37 +1808,25 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2275,102 +2243,50 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:5">
-      <c r="A2" s="65" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="65" t="s">
         <v>7</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:5">
-      <c r="A3" s="68" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="70" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>8</v>
-      </c>
+      <c r="A3" s="66"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="41"/>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="72" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>9</v>
-      </c>
+      <c r="A4" s="66"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="44"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="68" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="73" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="74" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
+      <c r="A5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="75" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="76" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
+      <c r="A6" s="66"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="70"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="77"/>
-      <c r="B7" s="77"/>
-      <c r="C7" s="77"/>
+      <c r="A7" s="71"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" display="5"/>
-    <hyperlink ref="D6" r:id="rId1" display="1"/>
-    <hyperlink ref="E7" r:id="rId1"/>
-    <hyperlink ref="D7" r:id="rId1"/>
     <hyperlink ref="D13" r:id="rId1"/>
     <hyperlink ref="D14" r:id="rId1"/>
     <hyperlink ref="D19" r:id="rId1"/>
@@ -2385,7 +2301,6 @@
     <hyperlink ref="E31" r:id="rId1"/>
     <hyperlink ref="D32" r:id="rId1"/>
     <hyperlink ref="E32" r:id="rId1"/>
-    <hyperlink ref="D8" r:id="rId1"/>
     <hyperlink ref="D10" r:id="rId1"/>
     <hyperlink ref="D12" r:id="rId1"/>
     <hyperlink ref="D16" r:id="rId1"/>
@@ -2403,7 +2318,6 @@
     <hyperlink ref="D27" r:id="rId1"/>
     <hyperlink ref="D29" r:id="rId1"/>
     <hyperlink ref="D33" r:id="rId1"/>
-    <hyperlink ref="A2" r:id="rId2" display="eclithor.com" tooltip="http://eclithor.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2424,77 +2338,77 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="55"/>
+      <c r="A2" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="54"/>
     </row>
     <row r="3" ht="15" spans="1:7">
-      <c r="A3" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="55"/>
+      <c r="A3" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="54"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="58" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="55"/>
+      <c r="A4" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="54"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="59" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="61"/>
+      <c r="A5" s="58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="58"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="61"/>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
+      <c r="A6" s="58"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="61"/>
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
+      <c r="A7" s="58"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="61"/>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
+      <c r="A8" s="58"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="F16" s="62" t="s">
-        <v>29</v>
-      </c>
-      <c r="G16" s="63" t="s">
-        <v>30</v>
+      <c r="F16" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="61" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="6:7">
-      <c r="F17" s="62" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" s="64" t="s">
-        <v>32</v>
+      <c r="F17" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="62" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2537,13 +2451,13 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="49"/>
+      <c r="A2" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="48"/>
       <c r="D2">
         <v>1</v>
       </c>
@@ -2552,13 +2466,13 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="49"/>
+      <c r="A3" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="48"/>
       <c r="D3">
         <v>2</v>
       </c>
@@ -2567,27 +2481,27 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="51"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="51"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="52"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="51"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="52"/>
+      <c r="A4" s="50"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+    </row>
+    <row r="5" ht="15" spans="1:6">
+      <c r="A5" s="50"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="51"/>
+    </row>
+    <row r="6" ht="15" spans="1:6">
+      <c r="A6" s="50"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="51"/>
     </row>
     <row r="7" spans="1:6">
       <c r="D7" s="46"/>
@@ -2648,10 +2562,10 @@
     <row r="2" ht="16.5" spans="1:5">
       <c r="A2" s="37"/>
       <c r="B2" s="38" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C2" s="39" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2663,10 +2577,10 @@
     <row r="3" ht="16.5" spans="1:5">
       <c r="A3" s="37"/>
       <c r="B3" s="40" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C3" s="41" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -2678,10 +2592,10 @@
     <row r="4" ht="16.5" spans="1:5">
       <c r="A4" s="42"/>
       <c r="B4" s="43" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -2745,7 +2659,7 @@
   <sheetData>
     <row r="1" ht="31.5" spans="1:10">
       <c r="A1" s="10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2756,141 +2670,141 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="5" ht="83" customHeight="1" spans="1:10">
       <c r="A5" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="J5" s="28"/>
     </row>
     <row r="6" ht="76" customHeight="1" spans="1:10">
       <c r="A6" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="7" ht="75" customHeight="1" spans="1:10">
       <c r="A7" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="8" ht="75" customHeight="1" spans="1:10">
       <c r="A8" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="9" ht="70" customHeight="1" spans="1:10">
       <c r="A9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="10" ht="97" customHeight="1" spans="1:10">
@@ -2911,7 +2825,7 @@
       <c r="F11" s="34"/>
       <c r="G11" s="34"/>
     </row>
-    <row r="12" ht="15.75" spans="1:10">
+    <row r="12" spans="1:10">
       <c r="A12" s="35"/>
       <c r="B12" s="36"/>
       <c r="C12" s="36"/>
@@ -2945,274 +2859,274 @@
   <sheetData>
     <row r="1" ht="31.5" spans="1:9">
       <c r="A1" s="10" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" ht="15" spans="1:9">
       <c r="A2" s="11"/>
     </row>
-    <row r="3" ht="27.75" spans="1:9">
+    <row r="3" ht="24.75" spans="1:9">
       <c r="A3" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="12" t="s">
         <v>81</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="4" ht="62" customHeight="1" spans="1:9">
       <c r="A4" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="H4" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="I4" s="15" t="s">
         <v>90</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="5" ht="49" customHeight="1" spans="1:9">
       <c r="A5" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="H5" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="I5" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="6" ht="67" customHeight="1" spans="1:9">
       <c r="A6" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="I6" s="15" t="s">
         <v>107</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="7" ht="65" customHeight="1" spans="1:9">
       <c r="A7" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="G7" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="H7" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="I7" s="15" t="s">
         <v>116</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="8" ht="64" customHeight="1" spans="1:9">
       <c r="A8" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="H8" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="I8" s="15" t="s">
         <v>124</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="9" ht="64" customHeight="1" spans="1:9">
       <c r="A9" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="H9" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="I9" s="15" t="s">
         <v>132</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="10" ht="59" customHeight="1" spans="1:9">
       <c r="A10" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="G10" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="H10" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="I10" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="D10" s="15" t="s">
+    </row>
+    <row r="11" ht="48.75" spans="1:9">
+      <c r="A11" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="B11" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="C11" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="D11" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="F11" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="G11" s="15" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="11" ht="54.75" spans="1:9">
-      <c r="A11" s="12" t="s">
+      <c r="H11" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="I11" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="C11" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:9">
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="23"/>
       <c r="B12" s="24"/>
       <c r="C12" s="24"/>
@@ -3243,143 +3157,143 @@
     <col min="7" max="7" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" spans="1:10">
+    <row r="1" ht="15" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" ht="94" customHeight="1" spans="1:10">
       <c r="A2" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="3" ht="57.75" spans="1:10">
+      <c r="A3" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="3" ht="66.75" spans="1:10">
-      <c r="A3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="J3" s="5"/>
     </row>
     <row r="4" ht="74" customHeight="1" spans="1:10">
       <c r="A4" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B4" s="3" t="s">
+    </row>
+    <row r="5" ht="57.75" spans="1:10">
+      <c r="A5" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>181</v>
-      </c>
-    </row>
-    <row r="5" ht="66.75" spans="1:10">
-      <c r="A5" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="6" ht="75" customHeight="1" spans="1:10">
       <c r="A6" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>194</v>
       </c>
     </row>
   </sheetData>
